--- a/scripts/tests/fixtures/evolution/workbook-200900001-month.xlsx
+++ b/scripts/tests/fixtures/evolution/workbook-200900001-month.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="122">
   <si>
     <t>{{report.title}}</t>
   </si>
@@ -79,7 +79,7 @@
     <t>Deposits</t>
   </si>
   <si>
-    <t>Withdrawals *</t>
+    <t>Withdrawals{{footnote.periods.withdrawals}}</t>
   </si>
   <si>
     <t>Net flows</t>
@@ -103,99 +103,114 @@
     <t>Realized on sales</t>
   </si>
   <si>
-    <t>Income *</t>
+    <t>Income{{footnote.periods.income}}</t>
   </si>
   <si>
     <t>Realized total</t>
   </si>
   <si>
-    <t>Fees *</t>
+    <t>Fees{{footnote.periods.fees}}</t>
+  </si>
+  <si>
+    <t>FX costs{{footnote.periods.fx_costs}}</t>
+  </si>
+  <si>
+    <t>Costs total</t>
+  </si>
+  <si>
+    <t>Cash movements</t>
+  </si>
+  <si>
+    <t>FX on cash</t>
+  </si>
+  <si>
+    <t>Unexplained</t>
+  </si>
+  <si>
+    <t>Priced</t>
+  </si>
+  <si>
+    <t>Unpriced</t>
+  </si>
+  <si>
+    <t>No rate</t>
+  </si>
+  <si>
+    <t>Missing rate</t>
+  </si>
+  <si>
+    <t>{{table:periods|period,period_start,period_end,portfolio_id,currency,invested_open,market_value_open,cash_open,unrealized_open,fx_unrealized_open,deposits,withdrawals,flows_net,purchases_at_cost,transfers_in_at_cost,sales_at_cost,transfers_out_at_cost,sales_proceeds,realized_sales,fx_realized,income,realized_total,fees,fx_costs,costs_total,cash_movements,fx_cash,invested_close,market_value_close,cash_close,unrealized_close,fx_unrealized_close,unexplained,priced_instruments,unpriced_instruments,unconverted,missing_rate}}</t>
+  </si>
+  <si>
+    <t>{{table:periods_notes|note}}</t>
+  </si>
+  <si>
+    <t>Net contributions</t>
+  </si>
+  <si>
+    <t>Income{{footnote.summary.income_total}}</t>
+  </si>
+  <si>
+    <t>Costs total{{footnote.summary.costs_total}}</t>
+  </si>
+  <si>
+    <t>Unrealized, start</t>
+  </si>
+  <si>
+    <t>Unrealized, end</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Plain return %</t>
+  </si>
+  <si>
+    <t>{{table:summary|portfolio_id,currency,net_contributions,realized_sales_total,fx_realized_total,income_total,realized_total,costs_total,fx_cash_total,unrealized_start,unrealized_end,fx_unrealized_end,performance,plain_return_pct}}</t>
+  </si>
+  <si>
+    <t>{{table:summary_notes|note}}</t>
+  </si>
+  <si>
+    <t>Invested at cost and market value, period by period</t>
+  </si>
+  <si>
+    <t>{{table:summary_series|portfolio_id,period,period_end,currency,invested_close,market_value_close}}</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>{{table:notes_facts|item,value}}</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>{{table:notes_facts_notes|note}}</t>
+  </si>
+  <si>
+    <t>Investment evolution — Fixture growth (conseq:200900001)</t>
+  </si>
+  <si>
+    <t>2025-07-01 – 2026-06-15 · by month · in CZK · average cost</t>
+  </si>
+  <si>
+    <t>Withdrawals</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Fees</t>
   </si>
   <si>
     <t>FX costs *</t>
   </si>
   <si>
-    <t>Costs total</t>
-  </si>
-  <si>
-    <t>Cash movements</t>
-  </si>
-  <si>
-    <t>FX on cash</t>
-  </si>
-  <si>
-    <t>Unexplained</t>
-  </si>
-  <si>
-    <t>Priced</t>
-  </si>
-  <si>
-    <t>Unpriced</t>
-  </si>
-  <si>
-    <t>No rate</t>
-  </si>
-  <si>
-    <t>Missing rate</t>
-  </si>
-  <si>
-    <t>{{table:periods|period,period_start,period_end,portfolio_id,currency,invested_open,market_value_open,cash_open,unrealized_open,fx_unrealized_open,deposits,withdrawals,flows_net,purchases_at_cost,transfers_in_at_cost,sales_at_cost,transfers_out_at_cost,sales_proceeds,realized_sales,fx_realized,income,realized_total,fees,fx_costs,costs_total,cash_movements,fx_cash,invested_close,market_value_close,cash_close,unrealized_close,fx_unrealized_close,unexplained,priced_instruments,unpriced_instruments,unconverted,missing_rate}}</t>
-  </si>
-  <si>
-    <t>{{table:periods_notes|note}}</t>
-  </si>
-  <si>
-    <t>Net contributions</t>
-  </si>
-  <si>
-    <t>Costs total *</t>
-  </si>
-  <si>
-    <t>Unrealized, start</t>
-  </si>
-  <si>
-    <t>Unrealized, end</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Plain return %</t>
-  </si>
-  <si>
-    <t>{{table:summary|portfolio_id,currency,net_contributions,realized_sales_total,fx_realized_total,income_total,realized_total,costs_total,fx_cash_total,unrealized_start,unrealized_end,fx_unrealized_end,performance,plain_return_pct}}</t>
-  </si>
-  <si>
-    <t>{{table:summary_notes|note}}</t>
-  </si>
-  <si>
-    <t>Invested at cost and market value, period by period</t>
-  </si>
-  <si>
-    <t>{{table:summary_series|portfolio_id,period,period_end,currency,invested_close,market_value_close}}</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>{{table:notes_facts|item,value}}</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>{{table:notes_facts_notes|note}}</t>
-  </si>
-  <si>
-    <t>Investment evolution — Fixture growth (conseq:200900001)</t>
-  </si>
-  <si>
-    <t>2025-07-01 – 2026-06-15 · by month · in CZK · average cost</t>
-  </si>
-  <si>
     <t>2025-07</t>
   </si>
   <si>
@@ -244,10 +259,10 @@
     <t>2026-06</t>
   </si>
   <si>
-    <t>* withdrawals — Conseq books an entry fee as a withdrawal beside its deposit; it stays inside withdrawals until the model carries each movement's description (IA-C49, IA-P4b).</t>
-  </si>
-  <si>
-    <t>* income, fees, fx_costs — 0: the model carries no fee and no description to tell them by, and none is inferred from an amount (IA-C49, IA-P4b).</t>
+    <t>withdrawals, fees, income — by the provider's label of each movement (income-labels.yaml, named on the Notes): Conseq's entry fees and commissions leave withdrawals for fees; income is what the table classes dividend, coupon or interest. A cash-leg fee or income is shown there too and stays in cash_movements — once: when the external-flow leg carries the same payment (a cash-account contract books a fee on both), the flow counts it.</t>
+  </si>
+  <si>
+    <t>* fx_costs — 0: the model carries no conversion fee, and none is inferred from an amount (IA-C49).</t>
   </si>
   <si>
     <t>fx_unrealized_open, fx_realized and fx_unrealized_close are the exchange-rate parts of the figures beside them — shown, never added to them.</t>
@@ -310,7 +325,7 @@
     <t>Income and fees</t>
   </si>
   <si>
-    <t>not available: the model carries no `fee`/`description`; fees, income and entry fees read 0, and entry fees stay inside withdrawals (IA-C49)</t>
+    <t>classified by income-labels.yaml v1 (14 labels); 0 of 7 cash and external-flow movements carry a label the table does not know, counted as other; 0 carry no label</t>
   </si>
   <si>
     <t>Exchange rates</t>
@@ -340,7 +355,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-15T08:00:00Z</t>
+    <t>2026-10-04T19:00:41Z</t>
   </si>
   <si>
     <t>As of 2026-06-15, by month; prices are the latest on or before each period end.</t>
@@ -349,7 +364,10 @@
     <t>Cost basis: average (REPORT_COST_BASIS).</t>
   </si>
   <si>
-    <t>Income and fees: not available: the model carries no `fee`/`description`; fees, income and entry fees read 0, and entry fees stay inside withdrawals (IA-C49).</t>
+    <t>Income and fees: classified by income-labels.yaml v1 (14 labels); 0 of 7 cash and external-flow movements carry a label the table does not know, counted as other; 0 carry no label.</t>
+  </si>
+  <si>
+    <t>Security-leg fees in the window: 1040.00 CZK — the provider's record of the entry fees that arrive as their own withdrawals (classified fee above); not added to fees again.</t>
   </si>
   <si>
     <t>Amounts are in CZK, each converted at its own day's rate from investment.fx_rate (the ČNB fixing via cnb-rates, IA-C68) — the latest rate on or before that day; an amount with no rate is never converted at a guess.</t>
@@ -494,12 +512,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -594,7 +612,7 @@
         <v>20</v>
       </c>
       <c r="L5" t="s" s="6">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="M5" t="s" s="6">
         <v>22</v>
@@ -621,16 +639,16 @@
         <v>19</v>
       </c>
       <c r="U5" t="s" s="6">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="V5" t="s" s="6">
         <v>30</v>
       </c>
       <c r="W5" t="s" s="6">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="X5" t="s" s="6">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="Y5" t="s" s="6">
         <v>33</v>
@@ -674,7 +692,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>45839.0</v>
@@ -683,10 +701,10 @@
         <v>45869.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>253800.0</v>
@@ -782,12 +800,12 @@
         <v>0.0</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>45839.0</v>
@@ -796,10 +814,10 @@
         <v>45869.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>253800.0</v>
@@ -895,12 +913,12 @@
         <v>0.0</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>45870.0</v>
@@ -909,10 +927,10 @@
         <v>45900.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>129800.0</v>
@@ -1008,12 +1026,12 @@
         <v>0.0</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>45870.0</v>
@@ -1022,10 +1040,10 @@
         <v>45900.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>129800.0</v>
@@ -1121,12 +1139,12 @@
         <v>0.0</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>45901.0</v>
@@ -1135,10 +1153,10 @@
         <v>45930.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>129800.0</v>
@@ -1234,12 +1252,12 @@
         <v>0.0</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>45901.0</v>
@@ -1248,10 +1266,10 @@
         <v>45930.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>129800.0</v>
@@ -1347,12 +1365,12 @@
         <v>0.0</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>45931.0</v>
@@ -1361,10 +1379,10 @@
         <v>45961.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>165200.0</v>
@@ -1460,12 +1478,12 @@
         <v>0.0</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>45931.0</v>
@@ -1474,10 +1492,10 @@
         <v>45961.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>165200.0</v>
@@ -1573,12 +1591,12 @@
         <v>0.0</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>45962.0</v>
@@ -1587,10 +1605,10 @@
         <v>45991.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>263200.0</v>
@@ -1686,12 +1704,12 @@
         <v>0.0</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>45962.0</v>
@@ -1700,10 +1718,10 @@
         <v>45991.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>263200.0</v>
@@ -1799,12 +1817,12 @@
         <v>0.0</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>45992.0</v>
@@ -1813,10 +1831,10 @@
         <v>46022.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>263200.0</v>
@@ -1870,13 +1888,13 @@
         <v>2760.0</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="X16" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="Z16" s="9" t="n">
         <v>-12275.0</v>
@@ -1912,12 +1930,12 @@
         <v>0.0</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>45992.0</v>
@@ -1926,10 +1944,10 @@
         <v>46022.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>263200.0</v>
@@ -1983,13 +2001,13 @@
         <v>2760.0</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="X17" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="Z17" s="9" t="n">
         <v>-12275.0</v>
@@ -2025,12 +2043,12 @@
         <v>0.0</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>46023.0</v>
@@ -2039,10 +2057,10 @@
         <v>46053.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>242200.0</v>
@@ -2138,12 +2156,12 @@
         <v>0.0</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>46023.0</v>
@@ -2152,10 +2170,10 @@
         <v>46053.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>242200.0</v>
@@ -2251,12 +2269,12 @@
         <v>0.0</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>46054.0</v>
@@ -2265,10 +2283,10 @@
         <v>46081.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>254550.0</v>
@@ -2364,12 +2382,12 @@
         <v>0.0</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>46054.0</v>
@@ -2378,10 +2396,10 @@
         <v>46081.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>254550.0</v>
@@ -2477,12 +2495,12 @@
         <v>0.0</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>46082.0</v>
@@ -2491,10 +2509,10 @@
         <v>46112.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>254550.0</v>
@@ -2590,12 +2608,12 @@
         <v>0.0</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>46082.0</v>
@@ -2604,10 +2622,10 @@
         <v>46112.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>254550.0</v>
@@ -2703,12 +2721,12 @@
         <v>0.0</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>46113.0</v>
@@ -2717,10 +2735,10 @@
         <v>46142.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>239490.0</v>
@@ -2816,12 +2834,12 @@
         <v>0.0</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>46113.0</v>
@@ -2830,10 +2848,10 @@
         <v>46142.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>239490.0</v>
@@ -2929,12 +2947,12 @@
         <v>0.0</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>46143.0</v>
@@ -2943,10 +2961,10 @@
         <v>46173.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>130423.33</v>
@@ -3000,13 +3018,13 @@
         <v>0.0</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="X26" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y26" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="Z26" s="9" t="n">
         <v>0.0</v>
@@ -3042,12 +3060,12 @@
         <v>0.0</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>46143.0</v>
@@ -3056,10 +3074,10 @@
         <v>46173.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>130423.33</v>
@@ -3113,13 +3131,13 @@
         <v>0.0</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="X27" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="Z27" s="9" t="n">
         <v>0.0</v>
@@ -3155,12 +3173,12 @@
         <v>0.0</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>46174.0</v>
@@ -3169,10 +3187,10 @@
         <v>46188.0</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>156423.33</v>
@@ -3268,12 +3286,12 @@
         <v>0.0</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>46174.0</v>
@@ -3282,10 +3300,10 @@
         <v>46188.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>156423.33</v>
@@ -3381,32 +3399,32 @@
         <v>0.0</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3437,12 +3455,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -3462,39 +3480,39 @@
         <v>19</v>
       </c>
       <c r="F4" t="s" s="6">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s" s="6">
         <v>30</v>
       </c>
       <c r="H4" t="s" s="6">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s" s="6">
         <v>35</v>
       </c>
       <c r="J4" t="s" s="6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s" s="6">
         <v>19</v>
       </c>
       <c r="M4" t="s" s="6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N4" t="s" s="6">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>28900.0</v>
@@ -3512,7 +3530,7 @@
         <v>24700.0</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.0</v>
+        <v>13515.0</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>125.0</v>
@@ -3527,18 +3545,18 @@
         <v>-540.0</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>26651.67</v>
+        <v>13136.67</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>12.882272</v>
+        <v>6.349701</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>28900.0</v>
@@ -3556,7 +3574,7 @@
         <v>24700.0</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.0</v>
+        <v>13515.0</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>125.0</v>
@@ -3571,30 +3589,30 @@
         <v>-540.0</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>26651.67</v>
+        <v>13136.67</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>12.882272</v>
+        <v>6.349701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -3619,16 +3637,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>45869.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>129800.0</v>
@@ -3639,16 +3657,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>45869.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>129800.0</v>
@@ -3659,16 +3677,16 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>45900.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>129800.0</v>
@@ -3679,16 +3697,16 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>45900.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>129800.0</v>
@@ -3699,16 +3717,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>45930.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>165200.0</v>
@@ -3719,16 +3737,16 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>45930.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>165200.0</v>
@@ -3739,16 +3757,16 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>45961.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>263200.0</v>
@@ -3759,16 +3777,16 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>45961.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>263200.0</v>
@@ -3779,16 +3797,16 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>45991.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>263200.0</v>
@@ -3799,16 +3817,16 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>45991.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>263200.0</v>
@@ -3819,16 +3837,16 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>46022.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>242200.0</v>
@@ -3839,16 +3857,16 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>46022.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>242200.0</v>
@@ -3859,16 +3877,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>46053.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>254550.0</v>
@@ -3879,16 +3897,16 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>46053.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>254550.0</v>
@@ -3899,16 +3917,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>46081.0</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>254550.0</v>
@@ -3919,16 +3937,16 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>46081.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>254550.0</v>
@@ -3939,16 +3957,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>46112.0</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>239490.0</v>
@@ -3959,16 +3977,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>46112.0</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>239490.0</v>
@@ -3979,16 +3997,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>46142.0</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>130423.33</v>
@@ -3999,16 +4017,16 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>46142.0</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E33" s="9" t="n">
         <v>130423.33</v>
@@ -4019,16 +4037,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>46173.0</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>156423.33</v>
@@ -4039,16 +4057,16 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>46173.0</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E35" s="9" t="n">
         <v>156423.33</v>
@@ -4059,16 +4077,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>46188.0</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>169623.33</v>
@@ -4079,16 +4097,16 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>46188.0</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E37" s="9" t="n">
         <v>169623.33</v>
@@ -4104,7 +4122,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="24.0"/>
@@ -4113,28 +4131,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s" s="5">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -4142,39 +4160,39 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -4182,103 +4200,108 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
